--- a/datos/fab_queso_bm.xlsx
+++ b/datos/fab_queso_bm.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/34bf2af71bbc2e43/Documentos/GitHub/master-queseria/website/datos/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="522" documentId="8_{DFAD049F-9521-4407-9131-61DB2BC601CF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{EBA12C51-02E6-49DB-A77E-6946DA9D2FAC}"/>
+  <xr:revisionPtr revIDLastSave="523" documentId="8_{DFAD049F-9521-4407-9131-61DB2BC601CF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{84BBB2D5-5D36-4712-9E9A-87D168DBD972}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="16440" xr2:uid="{15E1F47D-7F01-4CFA-AA86-2CDB7CC433C5}"/>
+    <workbookView xWindow="3075" yWindow="1950" windowWidth="23595" windowHeight="14250" xr2:uid="{15E1F47D-7F01-4CFA-AA86-2CDB7CC433C5}"/>
   </bookViews>
   <sheets>
     <sheet name="fab_queso_bm" sheetId="1" r:id="rId1"/>
@@ -21,7 +21,7 @@
   </sheets>
   <calcPr calcId="191029"/>
   <pivotCaches>
-    <pivotCache cacheId="1" r:id="rId6"/>
+    <pivotCache cacheId="0" r:id="rId6"/>
   </pivotCaches>
   <extLst>
     <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
@@ -174,10 +174,10 @@
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr9="http://schemas.microsoft.com/office/spreadsheetml/2016/revision9" mc:Ignorable="x14ac x16r2 xr xr9">
   <numFmts count="2">
     <numFmt numFmtId="164" formatCode="0.0%"/>
-    <numFmt numFmtId="166" formatCode="0.000"/>
+    <numFmt numFmtId="165" formatCode="0.000"/>
   </numFmts>
   <fonts count="19" x14ac:knownFonts="1">
     <font>
@@ -662,7 +662,7 @@
     <xf numFmtId="0" fontId="1" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="1" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="10">
+  <cellXfs count="9">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" pivotButton="1"/>
@@ -679,8 +679,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="left" indent="2"/>
     </xf>
-    <xf numFmtId="166" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="42">
     <cellStyle name="20% - Énfasis1" xfId="19" builtinId="30" customBuiltin="1"/>
@@ -727,9 +726,6 @@
     <cellStyle name="Total" xfId="17" builtinId="25" customBuiltin="1"/>
   </cellStyles>
   <dxfs count="18">
-    <dxf>
-      <numFmt numFmtId="166" formatCode="0.000"/>
-    </dxf>
     <dxf>
       <alignment horizontal="center"/>
     </dxf>
@@ -779,10 +775,15 @@
       <numFmt numFmtId="0" formatCode="General"/>
     </dxf>
     <dxf>
+      <numFmt numFmtId="165" formatCode="0.000"/>
+    </dxf>
+    <dxf>
       <numFmt numFmtId="19" formatCode="dd/mm/yyyy"/>
     </dxf>
   </dxfs>
-  <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
+  <tableStyles count="1" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16">
+    <tableStyle name="Invisible" pivot="0" table="0" count="0" xr9:uid="{4822773B-CB01-4976-972F-3645758B7F8F}"/>
+  </tableStyles>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
       <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
@@ -7240,10 +7241,6 @@
 </xdr:wsDr>
 </file>
 
-<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
-<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
-</file>
-
 <file path=xl/pivotCache/pivotCacheDefinition1.xml><?xml version="1.0" encoding="utf-8"?>
 <pivotCacheDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" r:id="rId1" refreshedBy="Juan Riera" refreshedDate="46013.700123726849" createdVersion="8" refreshedVersion="8" minRefreshableVersion="3" recordCount="45" xr:uid="{30129B98-EFB0-49A7-9A3E-AE8AAEB0B5CA}">
   <cacheSource type="worksheet">
@@ -9067,7 +9064,7 @@
 </file>
 
 <file path=xl/pivotTables/pivotTable1.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{0604FA9A-F2B6-421C-9331-9DB7EBCD432E}" name="TablaDinámica1" cacheId="1" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Valores" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" chartFormat="4">
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{0604FA9A-F2B6-421C-9331-9DB7EBCD432E}" name="TablaDinámica1" cacheId="0" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Valores" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" chartFormat="4">
   <location ref="A3:B15" firstHeaderRow="1" firstDataRow="1" firstDataCol="1" rowPageCount="1" colPageCount="1"/>
   <pivotFields count="31">
     <pivotField numFmtId="14" showAll="0">
@@ -9264,7 +9261,7 @@
 </file>
 
 <file path=xl/pivotTables/pivotTable2.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{E2DC14DA-93E8-4457-97B2-DA3497AE7253}" name="TablaDinámica1" cacheId="1" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Valores" showError="1" updatedVersion="8" minRefreshableVersion="3" showDrill="0" itemPrintTitles="1" createdVersion="8" indent="0" showHeaders="0" outline="1" outlineData="1" multipleFieldFilters="0" chartFormat="4">
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{E2DC14DA-93E8-4457-97B2-DA3497AE7253}" name="TablaDinámica1" cacheId="0" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Valores" showError="1" updatedVersion="8" minRefreshableVersion="3" showDrill="0" itemPrintTitles="1" createdVersion="8" indent="0" showHeaders="0" outline="1" outlineData="1" multipleFieldFilters="0" chartFormat="4">
   <location ref="A3:C22" firstHeaderRow="0" firstDataRow="1" firstDataCol="1" rowPageCount="1" colPageCount="1"/>
   <pivotFields count="31">
     <pivotField numFmtId="14" showAll="0">
@@ -9843,16 +9840,6 @@
     <dataField name="coef  recup mp" fld="27" baseField="0" baseItem="1" numFmtId="164"/>
   </dataFields>
   <formats count="3">
-    <format dxfId="9">
-      <pivotArea dataOnly="0" labelOnly="1" outline="0" fieldPosition="0">
-        <references count="1">
-          <reference field="4294967294" count="2">
-            <x v="0"/>
-            <x v="1"/>
-          </reference>
-        </references>
-      </pivotArea>
-    </format>
     <format dxfId="8">
       <pivotArea dataOnly="0" labelOnly="1" outline="0" fieldPosition="0">
         <references count="1">
@@ -9864,6 +9851,16 @@
       </pivotArea>
     </format>
     <format dxfId="7">
+      <pivotArea dataOnly="0" labelOnly="1" outline="0" fieldPosition="0">
+        <references count="1">
+          <reference field="4294967294" count="2">
+            <x v="0"/>
+            <x v="1"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </format>
+    <format dxfId="6">
       <pivotArea dataOnly="0" labelOnly="1" outline="0" fieldPosition="0">
         <references count="1">
           <reference field="4294967294" count="2">
@@ -9907,7 +9904,7 @@
 </file>
 
 <file path=xl/pivotTables/pivotTable3.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{71593EB6-A148-4F59-BB01-DC54A5F356E9}" name="TablaDinámica1" cacheId="1" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Valores" showError="1" updatedVersion="8" minRefreshableVersion="3" showDrill="0" itemPrintTitles="1" createdVersion="8" indent="0" showHeaders="0" outline="1" outlineData="1" multipleFieldFilters="0" chartFormat="5">
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{71593EB6-A148-4F59-BB01-DC54A5F356E9}" name="TablaDinámica1" cacheId="0" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Valores" showError="1" updatedVersion="8" minRefreshableVersion="3" showDrill="0" itemPrintTitles="1" createdVersion="8" indent="0" showHeaders="0" outline="1" outlineData="1" multipleFieldFilters="0" chartFormat="5">
   <location ref="A3:C16" firstHeaderRow="0" firstDataRow="1" firstDataCol="1" rowPageCount="1" colPageCount="1"/>
   <pivotFields count="31">
     <pivotField numFmtId="14" showAll="0">
@@ -10468,16 +10465,6 @@
     <dataField name="coef  recup mp" fld="27" baseField="0" baseItem="1" numFmtId="164"/>
   </dataFields>
   <formats count="3">
-    <format dxfId="6">
-      <pivotArea dataOnly="0" labelOnly="1" outline="0" fieldPosition="0">
-        <references count="1">
-          <reference field="4294967294" count="2">
-            <x v="0"/>
-            <x v="1"/>
-          </reference>
-        </references>
-      </pivotArea>
-    </format>
     <format dxfId="5">
       <pivotArea dataOnly="0" labelOnly="1" outline="0" fieldPosition="0">
         <references count="1">
@@ -10489,6 +10476,16 @@
       </pivotArea>
     </format>
     <format dxfId="4">
+      <pivotArea dataOnly="0" labelOnly="1" outline="0" fieldPosition="0">
+        <references count="1">
+          <reference field="4294967294" count="2">
+            <x v="0"/>
+            <x v="1"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </format>
+    <format dxfId="3">
       <pivotArea dataOnly="0" labelOnly="1" outline="0" fieldPosition="0">
         <references count="1">
           <reference field="4294967294" count="2">
@@ -10550,7 +10547,7 @@
 </file>
 
 <file path=xl/pivotTables/pivotTable4.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{CF31340A-3564-414C-ACF4-66C1F2EFD181}" name="TablaDinámica1" cacheId="1" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Valores" showError="1" updatedVersion="8" minRefreshableVersion="3" showDrill="0" itemPrintTitles="1" createdVersion="8" indent="0" showHeaders="0" outline="1" outlineData="1" multipleFieldFilters="0" chartFormat="6">
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{CF31340A-3564-414C-ACF4-66C1F2EFD181}" name="TablaDinámica1" cacheId="0" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Valores" showError="1" updatedVersion="8" minRefreshableVersion="3" showDrill="0" itemPrintTitles="1" createdVersion="8" indent="0" showHeaders="0" outline="1" outlineData="1" multipleFieldFilters="0" chartFormat="6">
   <location ref="A3:C16" firstHeaderRow="0" firstDataRow="1" firstDataCol="1" rowPageCount="1" colPageCount="1"/>
   <pivotFields count="31">
     <pivotField numFmtId="14" showAll="0">
@@ -11111,16 +11108,6 @@
     <dataField name="coef  recup mp" fld="27" baseField="0" baseItem="1" numFmtId="164"/>
   </dataFields>
   <formats count="3">
-    <format dxfId="3">
-      <pivotArea dataOnly="0" labelOnly="1" outline="0" fieldPosition="0">
-        <references count="1">
-          <reference field="4294967294" count="2">
-            <x v="0"/>
-            <x v="1"/>
-          </reference>
-        </references>
-      </pivotArea>
-    </format>
     <format dxfId="2">
       <pivotArea dataOnly="0" labelOnly="1" outline="0" fieldPosition="0">
         <references count="1">
@@ -11132,6 +11119,16 @@
       </pivotArea>
     </format>
     <format dxfId="1">
+      <pivotArea dataOnly="0" labelOnly="1" outline="0" fieldPosition="0">
+        <references count="1">
+          <reference field="4294967294" count="2">
+            <x v="0"/>
+            <x v="1"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </format>
+    <format dxfId="0">
       <pivotArea dataOnly="0" labelOnly="1" outline="0" fieldPosition="0">
         <references count="1">
           <reference field="4294967294" count="2">
@@ -11221,7 +11218,7 @@
     <tableColumn id="5" xr3:uid="{38A4A279-7280-419F-8359-B6FE1BBECD05}" name="mg_past"/>
     <tableColumn id="6" xr3:uid="{ECC243D9-44AC-4E39-A370-06F6F92C67DC}" name="mp_past"/>
     <tableColumn id="7" xr3:uid="{B3949886-901D-42E3-B6E1-370C2060A463}" name="kg_cuba"/>
-    <tableColumn id="8" xr3:uid="{03447032-124D-4550-8388-8B29DAFB4656}" name="dens_cuba" dataDxfId="0"/>
+    <tableColumn id="8" xr3:uid="{03447032-124D-4550-8388-8B29DAFB4656}" name="dens_cuba" dataDxfId="16"/>
     <tableColumn id="10" xr3:uid="{DBF1BA18-52EB-462F-92B1-14B61E63489D}" name="est_cuba"/>
     <tableColumn id="11" xr3:uid="{006077DF-22A8-4EF6-9C11-9C52B8A4EB6B}" name="mg_cuba"/>
     <tableColumn id="12" xr3:uid="{0DE50DBD-0E29-4E48-8260-74ECFF948784}" name="mp_cuba"/>
@@ -11231,25 +11228,25 @@
     <tableColumn id="16" xr3:uid="{C1123D60-8BB8-450F-960C-73C409ADDBE0}" name="ph_salida_salmuera"/>
     <tableColumn id="44" xr3:uid="{CEFA638F-8BB8-4219-AED1-72485D0F3FA0}" name="peso_queso_total"/>
     <tableColumn id="43" xr3:uid="{F09CD882-8288-4113-8E25-63A928AD9ABB}" name="sal_queso"/>
-    <tableColumn id="17" xr3:uid="{0CAA2358-A593-48A6-BA64-3DC875DFEA60}" name="est_kg_cuba" dataDxfId="16">
+    <tableColumn id="17" xr3:uid="{0CAA2358-A593-48A6-BA64-3DC875DFEA60}" name="est_kg_cuba" dataDxfId="15">
       <calculatedColumnFormula>Tabla1[[#This Row],[est_past]]*Tabla1[[#This Row],[litros_past]]/100</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="18" xr3:uid="{6ED23833-8FF5-4139-8146-6BDCB16BFBDF}" name="mg_kg_cuba" dataDxfId="15">
+    <tableColumn id="18" xr3:uid="{6ED23833-8FF5-4139-8146-6BDCB16BFBDF}" name="mg_kg_cuba" dataDxfId="14">
       <calculatedColumnFormula>Tabla1[[#This Row],[mg_past]]*Tabla1[[#This Row],[litros_past]]/100</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="19" xr3:uid="{E5134140-5624-413D-858A-643A1A49ECC5}" name="mp_kg_cuba" dataDxfId="14">
+    <tableColumn id="19" xr3:uid="{E5134140-5624-413D-858A-643A1A49ECC5}" name="mp_kg_cuba" dataDxfId="13">
       <calculatedColumnFormula>Tabla1[[#This Row],[mp_past]]*Tabla1[[#This Row],[litros_past]]/100</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="20" xr3:uid="{F5931655-6B22-4D64-B01F-886346436C72}" name="est_kg_queso" dataDxfId="13">
+    <tableColumn id="20" xr3:uid="{F5931655-6B22-4D64-B01F-886346436C72}" name="est_kg_queso" dataDxfId="12">
       <calculatedColumnFormula>Tabla1[[#This Row],[est_salida_salmuera]]*Tabla1[[#This Row],[peso_queso_total]]/100</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="21" xr3:uid="{61B1D0DB-2291-4388-9B30-06AAECA9400D}" name="mg_kg_queso" dataDxfId="12">
+    <tableColumn id="21" xr3:uid="{61B1D0DB-2291-4388-9B30-06AAECA9400D}" name="mg_kg_queso" dataDxfId="11">
       <calculatedColumnFormula>Tabla1[[#This Row],[mg_salida_salmuera]]*Tabla1[[#This Row],[peso_queso_total]]/100</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="22" xr3:uid="{03726673-4D9D-4F1D-A8B9-2563B0267330}" name="esm_kg_queso" dataDxfId="11">
+    <tableColumn id="22" xr3:uid="{03726673-4D9D-4F1D-A8B9-2563B0267330}" name="esm_kg_queso" dataDxfId="10">
       <calculatedColumnFormula>(Tabla1[[#This Row],[est_kg_queso]]-Tabla1[[#This Row],[mg_kg_queso]])</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="23" xr3:uid="{80225C17-32BA-4E21-B7C8-90209AA1167A}" name="semana" dataDxfId="10">
+    <tableColumn id="23" xr3:uid="{80225C17-32BA-4E21-B7C8-90209AA1167A}" name="semana" dataDxfId="9">
       <calculatedColumnFormula>_xlfn.ISOWEEKNUM(Tabla1[[#This Row],[fecha]])</calculatedColumnFormula>
     </tableColumn>
   </tableColumns>
@@ -15342,13 +15339,12 @@
       <c r="A4" s="3" t="s">
         <v>38</v>
       </c>
-      <c r="B4" s="9"/>
     </row>
     <row r="5" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A5" s="5">
         <v>8</v>
       </c>
-      <c r="B5" s="9">
+      <c r="B5">
         <v>1.03</v>
       </c>
     </row>
@@ -15356,13 +15352,12 @@
       <c r="A6" s="3" t="s">
         <v>31</v>
       </c>
-      <c r="B6" s="9"/>
     </row>
     <row r="7" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A7" s="5">
         <v>9</v>
       </c>
-      <c r="B7" s="9">
+      <c r="B7">
         <v>1.0349999999999999</v>
       </c>
     </row>
@@ -15370,7 +15365,7 @@
       <c r="A8" s="5">
         <v>10</v>
       </c>
-      <c r="B8" s="9">
+      <c r="B8">
         <v>1.032</v>
       </c>
     </row>
@@ -15378,7 +15373,7 @@
       <c r="A9" s="5">
         <v>11</v>
       </c>
-      <c r="B9" s="9">
+      <c r="B9">
         <v>1.0314999999999999</v>
       </c>
     </row>
@@ -15386,13 +15381,12 @@
       <c r="A10" s="3" t="s">
         <v>33</v>
       </c>
-      <c r="B10" s="9"/>
     </row>
     <row r="11" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A11" s="5">
         <v>19</v>
       </c>
-      <c r="B11" s="9">
+      <c r="B11">
         <v>1.0335000000000001</v>
       </c>
     </row>
@@ -15400,7 +15394,7 @@
       <c r="A12" s="5">
         <v>20</v>
       </c>
-      <c r="B12" s="9">
+      <c r="B12">
         <v>1.03</v>
       </c>
     </row>
@@ -15408,7 +15402,7 @@
       <c r="A13" s="5">
         <v>21</v>
       </c>
-      <c r="B13" s="9">
+      <c r="B13">
         <v>1.0314999999999999</v>
       </c>
     </row>
@@ -15416,7 +15410,7 @@
       <c r="A14" s="5">
         <v>22</v>
       </c>
-      <c r="B14" s="9">
+      <c r="B14">
         <v>1.032</v>
       </c>
     </row>
@@ -15424,7 +15418,7 @@
       <c r="A15" s="3" t="s">
         <v>30</v>
       </c>
-      <c r="B15" s="9">
+      <c r="B15">
         <v>1.0319999999999998</v>
       </c>
     </row>
